--- a/testfiles/Categorias y Leyenda.xlsx
+++ b/testfiles/Categorias y Leyenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\GitHub\Savia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F53D192-8F58-4515-AF8F-A78CE6FDEDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{727AE282-CA1B-4235-972C-42BA09122038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C8D2E161-7CB4-40AE-9148-56308E86FC7D}"/>
   </bookViews>
@@ -89,12 +89,6 @@
     <t>13   Condicional de no nulidad</t>
   </si>
   <si>
-    <t>1 Reglas Nulas</t>
-  </si>
-  <si>
-    <t>1,1 Reglas No Nulas</t>
-  </si>
-  <si>
     <t>2 Tipos de Variable</t>
   </si>
   <si>
@@ -180,13 +174,19 @@
   </si>
   <si>
     <t>PROPUESTA TITULOS</t>
+  </si>
+  <si>
+    <t>1 Reglas No Nulas</t>
+  </si>
+  <si>
+    <t>1,1 Reglas Nulas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,6 +204,14 @@
     <font>
       <b/>
       <sz val="15"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -251,11 +259,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -603,7 +612,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
@@ -614,10 +623,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -625,10 +634,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -636,21 +645,21 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
+      <c r="B5" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -658,10 +667,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -669,10 +678,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -680,10 +689,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -691,10 +700,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -702,10 +711,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -713,10 +722,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -724,10 +733,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -735,10 +744,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -746,10 +755,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -757,10 +766,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -768,10 +777,10 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
